--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T11:00:33+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T11:53:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:53:44+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T12:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T12:55:48+01:00</t>
+    <t>2026-03-18T17:09:19+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$147</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4990" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4799" uniqueCount="647">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T11:10:04+02:00</t>
+    <t>2026-06-24T16:51:19+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -812,7 +812,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://loinc.org"/&gt;
   &lt;code value="8302-2"/&gt;
-  &lt;display value="Body height"/&gt;
+  &lt;display value="Körperlänge"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -943,7 +943,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://loinc.org"/&gt;
   &lt;code value="89269-5"/&gt;
-  &lt;display value="Body height Measured --at birth"/&gt;
+  &lt;display value="Körperlänge, gemessen --bei Geburt"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -980,7 +980,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
   &lt;code value="1153637007"/&gt;
-  &lt;display value="Body height (observable entity)"/&gt;
+  &lt;display value="Körperlänge"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -1148,38 +1148,20 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.kbv.de/StructureDefinition/KBV_PR_WEST_Encounter|1.0.0-kommentierung)
+    <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
-    <t>Begegnung</t>
-  </si>
-  <si>
-    <t>Referenz zur Ressource Begegnung</t>
+    <t>Healthcare event during which this observation is made</t>
+  </si>
+  <si>
+    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
   </si>
   <si>
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
-  </si>
-  <si>
-    <t>Observation.encounter.id</t>
-  </si>
-  <si>
-    <t>Observation.encounter.extension</t>
-  </si>
-  <si>
-    <t>Observation.encounter.reference</t>
-  </si>
-  <si>
-    <t>Observation.encounter.type</t>
-  </si>
-  <si>
-    <t>Observation.encounter.identifier</t>
-  </si>
-  <si>
-    <t>Observation.encounter.display</t>
   </si>
   <si>
     <t>Observation.effective[x]</t>
@@ -1282,6 +1264,11 @@
     <t>valueQuantity</t>
   </si>
   <si>
+    <t>&lt;valueQuantity xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://unitsofmeasure.org"/&gt;
+&lt;/valueQuantity&gt;</t>
+  </si>
+  <si>
     <t>http://fhir.de/ValueSet/VitalSignDE_Body_Length_UCUM</t>
   </si>
   <si>
@@ -1364,9 +1351,6 @@
     <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
   </si>
   <si>
-    <t>centimeter</t>
-  </si>
-  <si>
     <t>Quantity.unit</t>
   </si>
   <si>
@@ -1411,9 +1395,6 @@
   </si>
   <si>
     <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>cm</t>
   </si>
   <si>
     <t>http://fhir.de/ValueSet/UcumVitalsCommonDE</t>
@@ -2389,7 +2370,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ153"/>
+  <dimension ref="A1:AJ147"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.15625" customWidth="true" bestFit="true"/>
@@ -8797,7 +8778,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>355</v>
       </c>
@@ -8813,10 +8794,10 @@
         <v>74</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>76</v>
@@ -8910,35 +8891,39 @@
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>76</v>
+        <v>363</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>97</v>
+        <v>364</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>98</v>
+        <v>365</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>76</v>
       </c>
@@ -8974,19 +8959,17 @@
         <v>76</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>76</v>
+        <v>370</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>100</v>
+        <v>362</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>74</v>
@@ -8995,52 +8978,56 @@
         <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>76</v>
+        <v>371</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="D65" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>103</v>
+        <v>364</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>104</v>
+        <v>365</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>105</v>
+        <v>374</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
       </c>
@@ -9076,39 +9063,39 @@
         <v>76</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>110</v>
+        <v>362</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>111</v>
+        <v>371</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9116,13 +9103,13 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>76</v>
@@ -9131,16 +9118,16 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>329</v>
+        <v>377</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>330</v>
+        <v>378</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9190,7 +9177,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
@@ -9199,7 +9186,7 @@
         <v>82</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>332</v>
+        <v>94</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>95</v>
@@ -9207,10 +9194,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9233,18 +9220,20 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>124</v>
+        <v>380</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>334</v>
+        <v>381</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>76</v>
       </c>
@@ -9268,13 +9257,13 @@
         <v>76</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>337</v>
+        <v>76</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>338</v>
+        <v>76</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>76</v>
@@ -9292,27 +9281,27 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>339</v>
+        <v>379</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>95</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9323,10 +9312,10 @@
         <v>74</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>76</v>
@@ -9335,18 +9324,20 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>193</v>
+        <v>385</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>342</v>
+        <v>387</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
       </c>
@@ -9382,19 +9373,17 @@
         <v>76</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>76</v>
+        <v>370</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>344</v>
+        <v>384</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
@@ -9403,20 +9392,22 @@
         <v>82</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>94</v>
+        <v>390</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>76</v>
       </c>
@@ -9425,10 +9416,10 @@
         <v>74</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>76</v>
@@ -9437,18 +9428,20 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>97</v>
+        <v>385</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>346</v>
+        <v>386</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>347</v>
+        <v>387</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>76</v>
       </c>
@@ -9457,7 +9450,7 @@
         <v>76</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>76</v>
@@ -9472,13 +9465,11 @@
         <v>76</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>76</v>
+        <v>394</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>76</v>
@@ -9496,7 +9487,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
@@ -9505,7 +9496,7 @@
         <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>94</v>
+        <v>390</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>95</v>
@@ -9513,46 +9504,42 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>369</v>
+        <v>76</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>370</v>
+        <v>97</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>371</v>
+        <v>98</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>76</v>
       </c>
@@ -9588,17 +9575,19 @@
         <v>76</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AC70" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>376</v>
+        <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>368</v>
+        <v>100</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>74</v>
@@ -9607,56 +9596,52 @@
         <v>82</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>377</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>369</v>
+        <v>102</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>370</v>
+        <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>371</v>
+        <v>104</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>380</v>
+        <v>105</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>76</v>
       </c>
@@ -9692,39 +9677,39 @@
         <v>76</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>368</v>
+        <v>110</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>377</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9732,13 +9717,13 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>76</v>
@@ -9747,18 +9732,20 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>118</v>
+        <v>401</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>76</v>
       </c>
@@ -9806,7 +9793,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>74</v>
@@ -9823,10 +9810,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9843,30 +9830,32 @@
         <v>76</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>386</v>
+        <v>162</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>202</v>
+        <v>273</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q73" s="2"/>
+      <c r="Q73" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="R73" t="s" s="2">
         <v>76</v>
       </c>
@@ -9886,13 +9875,13 @@
         <v>76</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>76</v>
+        <v>413</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>76</v>
+        <v>414</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>76</v>
@@ -9910,27 +9899,27 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>204</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9938,7 +9927,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>82</v>
@@ -9953,19 +9942,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>391</v>
+        <v>97</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>394</v>
+        <v>273</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>76</v>
@@ -10002,17 +9991,19 @@
         <v>76</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AC74" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>376</v>
+        <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>390</v>
+        <v>421</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>74</v>
@@ -10021,7 +10012,7 @@
         <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>396</v>
+        <v>94</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>95</v>
@@ -10029,20 +10020,18 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>82</v>
@@ -10057,19 +10046,19 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>391</v>
+        <v>124</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>392</v>
+        <v>424</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>393</v>
+        <v>425</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>76</v>
@@ -10079,7 +10068,7 @@
         <v>76</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>76</v>
+        <v>428</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>76</v>
@@ -10094,11 +10083,13 @@
         <v>76</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z75" t="s" s="2">
-        <v>399</v>
+        <v>76</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>76</v>
@@ -10116,7 +10107,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>390</v>
+        <v>429</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
@@ -10125,18 +10116,18 @@
         <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>396</v>
+        <v>430</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10144,31 +10135,35 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>98</v>
+        <v>433</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>76</v>
       </c>
@@ -10192,13 +10187,11 @@
         <v>76</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>76</v>
+        <v>436</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>76</v>
@@ -10216,7 +10209,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>100</v>
+        <v>437</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>74</v>
@@ -10225,29 +10218,29 @@
         <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>403</v>
+        <v>438</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>76</v>
@@ -10259,18 +10252,20 @@
         <v>76</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>104</v>
+        <v>439</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>105</v>
+        <v>440</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>76</v>
       </c>
@@ -10294,86 +10289,86 @@
         <v>76</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>76</v>
+        <v>443</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>76</v>
+        <v>444</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>110</v>
+        <v>438</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>94</v>
+        <v>445</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>404</v>
+        <v>446</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>76</v>
+        <v>447</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>406</v>
+        <v>220</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>408</v>
+        <v>449</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>410</v>
+        <v>451</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>76</v>
@@ -10398,13 +10393,13 @@
         <v>76</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>76</v>
+        <v>452</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>76</v>
+        <v>453</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>76</v>
@@ -10422,13 +10417,13 @@
         <v>76</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>94</v>
@@ -10437,12 +10432,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>412</v>
+        <v>454</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10453,38 +10448,36 @@
         <v>74</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>162</v>
+        <v>455</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>414</v>
+        <v>456</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>415</v>
+        <v>457</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>273</v>
+        <v>458</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>416</v>
+        <v>459</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q79" t="s" s="2">
-        <v>417</v>
-      </c>
+      <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
         <v>76</v>
       </c>
@@ -10504,13 +10497,13 @@
         <v>76</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>418</v>
+        <v>76</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>419</v>
+        <v>76</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>76</v>
@@ -10528,13 +10521,13 @@
         <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>94</v>
@@ -10543,12 +10536,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10556,41 +10549,37 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>423</v>
+        <v>98</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>426</v>
+        <v>76</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>76</v>
@@ -10632,7 +10621,7 @@
         <v>76</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>427</v>
+        <v>100</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>74</v>
@@ -10641,63 +10630,61 @@
         <v>82</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>428</v>
+        <v>461</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>430</v>
+        <v>104</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>431</v>
+        <v>105</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>434</v>
+        <v>76</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>434</v>
+        <v>76</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>76</v>
@@ -10724,39 +10711,39 @@
         <v>76</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>435</v>
+        <v>110</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>436</v>
+        <v>94</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10764,7 +10751,7 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>82</v>
@@ -10779,20 +10766,18 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>162</v>
+        <v>463</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>424</v>
+        <v>465</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>76</v>
       </c>
@@ -10801,7 +10786,7 @@
         <v>76</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>442</v>
+        <v>76</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>76</v>
@@ -10816,29 +10801,29 @@
         <v>76</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>443</v>
+        <v>76</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="AC82" s="2"/>
       <c r="AD82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>76</v>
+        <v>370</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>74</v>
@@ -10853,14 +10838,16 @@
         <v>95</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="D83" t="s" s="2">
         <v>76</v>
       </c>
@@ -10869,32 +10856,30 @@
         <v>74</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>220</v>
+        <v>470</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>447</v>
+        <v>471</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>76</v>
       </c>
@@ -10918,13 +10903,13 @@
         <v>76</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>450</v>
+        <v>76</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>451</v>
+        <v>76</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>76</v>
@@ -10942,7 +10927,7 @@
         <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>74</v>
@@ -10951,7 +10936,7 @@
         <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>452</v>
+        <v>94</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>95</v>
@@ -10959,21 +10944,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>454</v>
+        <v>76</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>76</v>
@@ -10985,20 +10970,16 @@
         <v>76</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>455</v>
+        <v>98</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>76</v>
       </c>
@@ -11022,13 +11003,13 @@
         <v>76</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>459</v>
+        <v>76</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>460</v>
+        <v>76</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>76</v>
@@ -11046,31 +11027,31 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>453</v>
+        <v>100</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -11080,7 +11061,7 @@
         <v>75</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>76</v>
@@ -11089,20 +11070,18 @@
         <v>76</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>462</v>
+        <v>103</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>463</v>
+        <v>104</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>464</v>
+        <v>105</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>76</v>
       </c>
@@ -11138,19 +11117,19 @@
         <v>76</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>461</v>
+        <v>110</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
@@ -11162,15 +11141,15 @@
         <v>94</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11178,30 +11157,32 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>76</v>
@@ -11250,7 +11231,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>100</v>
+        <v>331</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -11259,29 +11240,29 @@
         <v>82</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>76</v>
+        <v>332</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>76</v>
@@ -11290,19 +11271,19 @@
         <v>76</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>104</v>
+        <v>334</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>105</v>
+        <v>335</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>106</v>
+        <v>336</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11328,51 +11309,51 @@
         <v>76</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>76</v>
+        <v>337</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>76</v>
+        <v>338</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>110</v>
+        <v>339</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11383,10 +11364,10 @@
         <v>74</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>76</v>
@@ -11395,16 +11376,16 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>470</v>
+        <v>193</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>471</v>
+        <v>341</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>472</v>
+        <v>342</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>473</v>
+        <v>343</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11442,17 +11423,19 @@
         <v>76</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AC88" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>376</v>
+        <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>474</v>
+        <v>344</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>74</v>
@@ -11467,16 +11450,14 @@
         <v>95</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>76</v>
       </c>
@@ -11485,10 +11466,10 @@
         <v>74</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>76</v>
@@ -11497,16 +11478,16 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>477</v>
+        <v>97</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>478</v>
+        <v>347</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>473</v>
+        <v>348</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11556,7 +11537,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>474</v>
+        <v>349</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
@@ -11571,14 +11552,16 @@
         <v>95</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C90" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="D90" t="s" s="2">
         <v>76</v>
       </c>
@@ -11590,24 +11573,26 @@
         <v>82</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>98</v>
+        <v>464</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>76</v>
@@ -11656,7 +11641,7 @@
         <v>76</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>100</v>
+        <v>467</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>74</v>
@@ -11665,51 +11650,49 @@
         <v>82</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>103</v>
+        <v>364</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>104</v>
+        <v>488</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>106</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>76</v>
@@ -11746,39 +11729,39 @@
         <v>76</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>110</v>
+        <v>490</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11801,16 +11784,16 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>97</v>
+        <v>492</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>328</v>
+        <v>493</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>329</v>
+        <v>494</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>330</v>
+        <v>495</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11860,27 +11843,27 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>331</v>
+        <v>496</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>332</v>
+        <v>94</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11891,28 +11874,28 @@
         <v>74</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>124</v>
+        <v>220</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>334</v>
+        <v>498</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>335</v>
+        <v>499</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>336</v>
+        <v>500</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11938,13 +11921,13 @@
         <v>76</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>337</v>
+        <v>501</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>338</v>
+        <v>502</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>76</v>
@@ -11962,7 +11945,7 @@
         <v>76</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>339</v>
+        <v>497</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>74</v>
@@ -11979,10 +11962,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11993,7 +11976,7 @@
         <v>74</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>76</v>
@@ -12002,20 +11985,18 @@
         <v>76</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>341</v>
+        <v>98</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>76</v>
@@ -12064,7 +12045,7 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>344</v>
+        <v>100</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>74</v>
@@ -12073,29 +12054,29 @@
         <v>82</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>76</v>
@@ -12104,19 +12085,19 @@
         <v>76</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>346</v>
+        <v>104</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>347</v>
+        <v>105</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>348</v>
+        <v>106</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12154,43 +12135,41 @@
         <v>76</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>349</v>
+        <v>110</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>76</v>
       </c>
@@ -12199,7 +12178,7 @@
         <v>74</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>83</v>
@@ -12211,18 +12190,20 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>471</v>
+        <v>243</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>493</v>
+        <v>244</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>76</v>
       </c>
@@ -12270,13 +12251,13 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>474</v>
+        <v>247</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>94</v>
@@ -12285,12 +12266,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12304,22 +12285,22 @@
         <v>82</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>370</v>
+        <v>97</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>495</v>
+        <v>98</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>496</v>
+        <v>99</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12370,7 +12351,7 @@
         <v>76</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>497</v>
+        <v>100</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>74</v>
@@ -12379,50 +12360,50 @@
         <v>82</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>499</v>
+        <v>103</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>500</v>
+        <v>104</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>501</v>
+        <v>105</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>502</v>
+        <v>106</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12460,39 +12441,39 @@
         <v>76</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>503</v>
+        <v>110</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12500,7 +12481,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>82</v>
@@ -12512,21 +12493,23 @@
         <v>76</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>505</v>
+        <v>258</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>506</v>
+        <v>259</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>76</v>
       </c>
@@ -12550,13 +12533,13 @@
         <v>76</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>508</v>
+        <v>76</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>509</v>
+        <v>76</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>76</v>
@@ -12574,7 +12557,7 @@
         <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>504</v>
+        <v>262</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>74</v>
@@ -12589,12 +12572,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12608,24 +12591,26 @@
         <v>82</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>98</v>
+        <v>265</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>76</v>
@@ -12674,7 +12659,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>100</v>
+        <v>268</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>74</v>
@@ -12683,52 +12668,54 @@
         <v>82</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>104</v>
+        <v>271</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>105</v>
+        <v>272</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>76</v>
       </c>
@@ -12764,39 +12751,39 @@
         <v>76</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12804,10 +12791,10 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>83</v>
@@ -12819,19 +12806,19 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>244</v>
+        <v>279</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>76</v>
@@ -12880,13 +12867,13 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>94</v>
@@ -12897,10 +12884,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12911,7 +12898,7 @@
         <v>74</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>76</v>
@@ -12920,19 +12907,23 @@
         <v>76</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>97</v>
+        <v>284</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>98</v>
+        <v>285</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>76</v>
       </c>
@@ -12980,7 +12971,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>100</v>
+        <v>289</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
@@ -12989,52 +12980,54 @@
         <v>82</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>105</v>
+        <v>514</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O104" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>76</v>
       </c>
@@ -13070,31 +13063,31 @@
         <v>76</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>110</v>
+        <v>318</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="105">
@@ -13110,7 +13103,7 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>82</v>
@@ -13122,22 +13115,22 @@
         <v>76</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>124</v>
+        <v>220</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>258</v>
+        <v>516</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>259</v>
+        <v>517</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>260</v>
+        <v>518</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>261</v>
+        <v>519</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>76</v>
@@ -13162,13 +13155,13 @@
         <v>76</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>76</v>
+        <v>520</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>76</v>
+        <v>521</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>76</v>
@@ -13186,7 +13179,7 @@
         <v>76</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>262</v>
+        <v>515</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>74</v>
@@ -13201,12 +13194,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13220,26 +13213,24 @@
         <v>82</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>265</v>
+        <v>98</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>76</v>
@@ -13288,7 +13279,7 @@
         <v>76</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>268</v>
+        <v>100</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>74</v>
@@ -13297,54 +13288,52 @@
         <v>82</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>271</v>
+        <v>104</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>76</v>
       </c>
@@ -13380,39 +13369,39 @@
         <v>76</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>275</v>
+        <v>110</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13420,10 +13409,10 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>83</v>
@@ -13435,19 +13424,19 @@
         <v>83</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>279</v>
+        <v>244</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>76</v>
@@ -13496,13 +13485,13 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>94</v>
@@ -13513,10 +13502,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13527,7 +13516,7 @@
         <v>74</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>76</v>
@@ -13536,23 +13525,19 @@
         <v>76</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>284</v>
+        <v>97</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>285</v>
+        <v>98</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>76</v>
       </c>
@@ -13600,7 +13585,7 @@
         <v>76</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>289</v>
+        <v>100</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>74</v>
@@ -13609,54 +13594,52 @@
         <v>82</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>314</v>
+        <v>104</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>521</v>
+        <v>105</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>76</v>
       </c>
@@ -13692,39 +13675,39 @@
         <v>76</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>318</v>
+        <v>110</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13732,7 +13715,7 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>82</v>
@@ -13744,22 +13727,22 @@
         <v>76</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>523</v>
+        <v>258</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>524</v>
+        <v>259</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>525</v>
+        <v>260</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>526</v>
+        <v>261</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>76</v>
@@ -13784,13 +13767,13 @@
         <v>76</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>527</v>
+        <v>76</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>528</v>
+        <v>76</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>76</v>
@@ -13808,7 +13791,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>522</v>
+        <v>262</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>74</v>
@@ -13823,12 +13806,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13842,24 +13825,26 @@
         <v>82</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>98</v>
+        <v>265</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>76</v>
@@ -13908,7 +13893,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>100</v>
+        <v>268</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -13917,52 +13902,54 @@
         <v>82</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>104</v>
+        <v>271</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>105</v>
+        <v>272</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>76</v>
       </c>
@@ -13998,39 +13985,39 @@
         <v>76</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14038,10 +14025,10 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>83</v>
@@ -14053,19 +14040,19 @@
         <v>83</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>244</v>
+        <v>279</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>76</v>
@@ -14114,13 +14101,13 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>94</v>
@@ -14131,10 +14118,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14145,7 +14132,7 @@
         <v>74</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>76</v>
@@ -14154,19 +14141,23 @@
         <v>76</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>97</v>
+        <v>284</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>98</v>
+        <v>285</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>76</v>
       </c>
@@ -14214,7 +14205,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>100</v>
+        <v>289</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
@@ -14223,52 +14214,54 @@
         <v>82</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>105</v>
+        <v>533</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>76</v>
       </c>
@@ -14304,34 +14297,34 @@
         <v>76</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>110</v>
+        <v>318</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
         <v>534</v>
       </c>
@@ -14344,35 +14337,33 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>124</v>
+        <v>535</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>258</v>
+        <v>536</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>259</v>
+        <v>537</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>76</v>
       </c>
@@ -14420,7 +14411,7 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>262</v>
+        <v>534</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
@@ -14432,15 +14423,15 @@
         <v>94</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>95</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14451,28 +14442,28 @@
         <v>74</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>97</v>
+        <v>540</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>265</v>
+        <v>541</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>266</v>
+        <v>542</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>267</v>
+        <v>543</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -14522,7 +14513,7 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>268</v>
+        <v>539</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
@@ -14534,15 +14525,15 @@
         <v>94</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>95</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14550,34 +14541,34 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>162</v>
+        <v>545</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>271</v>
+        <v>546</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>272</v>
+        <v>547</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>273</v>
+        <v>548</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>274</v>
+        <v>549</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>76</v>
@@ -14626,27 +14617,27 @@
         <v>76</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>275</v>
+        <v>544</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>95</v>
+        <v>550</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14654,35 +14645,31 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K120" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>278</v>
+        <v>98</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>76</v>
       </c>
@@ -14730,7 +14717,7 @@
         <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>281</v>
+        <v>100</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>74</v>
@@ -14739,29 +14726,29 @@
         <v>82</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>76</v>
@@ -14770,23 +14757,21 @@
         <v>76</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>284</v>
+        <v>103</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>285</v>
+        <v>104</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>286</v>
+        <v>105</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>76</v>
       </c>
@@ -14822,74 +14807,74 @@
         <v>76</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>289</v>
+        <v>110</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>76</v>
+        <v>554</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I122" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="J122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>314</v>
+        <v>555</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>316</v>
+        <v>106</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>317</v>
+        <v>190</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>76</v>
@@ -14938,27 +14923,27 @@
         <v>76</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>318</v>
+        <v>557</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14969,7 +14954,7 @@
         <v>74</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>76</v>
@@ -14981,16 +14966,16 @@
         <v>76</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -15040,7 +15025,7 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>74</v>
@@ -15049,18 +15034,18 @@
         <v>82</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>94</v>
+        <v>563</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>204</v>
+        <v>564</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15071,7 +15056,7 @@
         <v>74</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>76</v>
@@ -15083,16 +15068,16 @@
         <v>76</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15142,7 +15127,7 @@
         <v>76</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
@@ -15151,18 +15136,18 @@
         <v>82</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>94</v>
+        <v>563</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>204</v>
+        <v>564</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15173,7 +15158,7 @@
         <v>74</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>76</v>
@@ -15185,19 +15170,19 @@
         <v>76</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>552</v>
+        <v>220</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>76</v>
@@ -15222,13 +15207,13 @@
         <v>76</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>76</v>
+        <v>573</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>76</v>
+        <v>574</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>76</v>
@@ -15246,27 +15231,27 @@
         <v>76</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>557</v>
+        <v>95</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15277,7 +15262,7 @@
         <v>74</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>76</v>
@@ -15289,16 +15274,20 @@
         <v>76</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>98</v>
+        <v>576</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>76</v>
       </c>
@@ -15322,13 +15311,13 @@
         <v>76</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>76</v>
+        <v>580</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>76</v>
+        <v>581</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>76</v>
@@ -15346,38 +15335,38 @@
         <v>76</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>100</v>
+        <v>575</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>76</v>
@@ -15389,18 +15378,20 @@
         <v>76</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>103</v>
+        <v>583</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>104</v>
+        <v>584</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>105</v>
+        <v>585</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O127" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>76</v>
       </c>
@@ -15436,75 +15427,73 @@
         <v>76</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>110</v>
+        <v>582</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>111</v>
+        <v>588</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>560</v>
+        <v>589</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>560</v>
+        <v>589</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>561</v>
+        <v>76</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>563</v>
+        <v>591</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>76</v>
       </c>
@@ -15552,27 +15541,27 @@
         <v>76</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>565</v>
+        <v>592</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>565</v>
+        <v>592</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15583,7 +15572,7 @@
         <v>74</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>76</v>
@@ -15592,19 +15581,19 @@
         <v>76</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>566</v>
+        <v>593</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>568</v>
+        <v>595</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>569</v>
+        <v>596</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -15654,27 +15643,27 @@
         <v>76</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>565</v>
+        <v>592</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>570</v>
+        <v>94</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>571</v>
+        <v>204</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15685,7 +15674,7 @@
         <v>74</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>76</v>
@@ -15694,19 +15683,19 @@
         <v>76</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>566</v>
+        <v>598</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>573</v>
+        <v>599</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>574</v>
+        <v>600</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>569</v>
+        <v>601</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -15756,27 +15745,27 @@
         <v>76</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>570</v>
+        <v>94</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>571</v>
+        <v>204</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>575</v>
+        <v>602</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>575</v>
+        <v>602</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15787,7 +15776,7 @@
         <v>74</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>76</v>
@@ -15796,22 +15785,22 @@
         <v>76</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>220</v>
+        <v>545</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>577</v>
+        <v>604</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>578</v>
+        <v>605</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>579</v>
+        <v>606</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>76</v>
@@ -15836,13 +15825,13 @@
         <v>76</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>166</v>
+        <v>76</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>580</v>
+        <v>76</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>581</v>
+        <v>76</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>76</v>
@@ -15860,27 +15849,27 @@
         <v>76</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>575</v>
+        <v>602</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>95</v>
+        <v>607</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>582</v>
+        <v>608</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>582</v>
+        <v>608</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15891,7 +15880,7 @@
         <v>74</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>76</v>
@@ -15903,20 +15892,16 @@
         <v>76</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>583</v>
+        <v>98</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>76</v>
       </c>
@@ -15940,13 +15925,13 @@
         <v>76</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>587</v>
+        <v>76</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>588</v>
+        <v>76</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>76</v>
@@ -15964,38 +15949,38 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>582</v>
+        <v>100</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>76</v>
@@ -16007,20 +15992,18 @@
         <v>76</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>590</v>
+        <v>103</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>591</v>
+        <v>104</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>592</v>
+        <v>105</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>76</v>
       </c>
@@ -16056,73 +16039,75 @@
         <v>76</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>589</v>
+        <v>110</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>595</v>
+        <v>111</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>76</v>
+        <v>554</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I134" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>597</v>
+        <v>555</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>598</v>
+        <v>556</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O134" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P134" t="s" s="2">
         <v>76</v>
       </c>
@@ -16170,27 +16155,27 @@
         <v>76</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>596</v>
+        <v>557</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16198,10 +16183,10 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>76</v>
@@ -16213,18 +16198,20 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>600</v>
+        <v>220</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="O135" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P135" t="s" s="2">
         <v>76</v>
       </c>
@@ -16248,13 +16235,13 @@
         <v>76</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>76</v>
+        <v>237</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>76</v>
@@ -16272,27 +16259,27 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>204</v>
+        <v>95</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16303,7 +16290,7 @@
         <v>74</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>76</v>
@@ -16315,18 +16302,20 @@
         <v>83</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O136" s="2"/>
+        <v>619</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P136" t="s" s="2">
         <v>76</v>
       </c>
@@ -16362,41 +16351,41 @@
         <v>76</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="AC136" s="2"/>
       <c r="AD136" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>204</v>
+        <v>95</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C137" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="D137" t="s" s="2">
         <v>76</v>
       </c>
@@ -16405,7 +16394,7 @@
         <v>74</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>76</v>
@@ -16417,19 +16406,19 @@
         <v>83</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>552</v>
+        <v>385</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>613</v>
+        <v>389</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>76</v>
@@ -16478,27 +16467,27 @@
         <v>76</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>614</v>
+        <v>95</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16595,10 +16584,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16697,45 +16686,45 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>561</v>
+        <v>76</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J140" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>103</v>
+        <v>401</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>562</v>
+        <v>402</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>563</v>
+        <v>627</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>106</v>
+        <v>404</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>190</v>
+        <v>405</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>76</v>
@@ -16784,27 +16773,27 @@
         <v>76</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>564</v>
+        <v>406</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16812,7 +16801,7 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G141" t="s" s="2">
         <v>82</v>
@@ -16821,30 +16810,32 @@
         <v>76</v>
       </c>
       <c r="I141" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J141" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>220</v>
+        <v>162</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>619</v>
+        <v>409</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>620</v>
+        <v>410</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>621</v>
+        <v>273</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>236</v>
+        <v>411</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q141" s="2"/>
+      <c r="Q141" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="R141" t="s" s="2">
         <v>76</v>
       </c>
@@ -16864,13 +16855,13 @@
         <v>76</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>237</v>
+        <v>413</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>238</v>
+        <v>414</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>76</v>
@@ -16888,10 +16879,10 @@
         <v>76</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>618</v>
+        <v>415</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>82</v>
@@ -16905,10 +16896,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16916,7 +16907,7 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>82</v>
@@ -16931,19 +16922,19 @@
         <v>83</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>623</v>
+        <v>97</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>624</v>
+        <v>418</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>626</v>
+        <v>273</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>76</v>
@@ -16980,17 +16971,19 @@
         <v>76</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AC142" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD142" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>622</v>
+        <v>421</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>74</v>
@@ -17007,20 +17000,18 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>634</v>
+      </c>
+      <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G143" t="s" s="2">
         <v>82</v>
@@ -17035,19 +17026,19 @@
         <v>83</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>391</v>
+        <v>124</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>624</v>
+        <v>424</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>626</v>
+        <v>426</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>76</v>
@@ -17057,7 +17048,7 @@
         <v>76</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>76</v>
+        <v>428</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>76</v>
@@ -17096,7 +17087,7 @@
         <v>76</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>622</v>
+        <v>429</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>74</v>
@@ -17105,7 +17096,7 @@
         <v>82</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>94</v>
+        <v>430</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>95</v>
@@ -17113,10 +17104,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17124,7 +17115,7 @@
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G144" t="s" s="2">
         <v>82</v>
@@ -17136,19 +17127,23 @@
         <v>76</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>98</v>
+        <v>433</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N144" s="2"/>
-      <c r="O144" s="2"/>
+        <v>638</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>76</v>
       </c>
@@ -17196,7 +17191,7 @@
         <v>76</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>100</v>
+        <v>437</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>74</v>
@@ -17205,29 +17200,29 @@
         <v>82</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>76</v>
@@ -17239,18 +17234,20 @@
         <v>76</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>104</v>
+        <v>640</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>105</v>
+        <v>641</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O145" s="2"/>
+        <v>642</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>76</v>
       </c>
@@ -17274,62 +17271,62 @@
         <v>76</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>76</v>
+        <v>443</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>76</v>
+        <v>444</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>110</v>
+        <v>639</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>94</v>
+        <v>445</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>111</v>
+        <v>95</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>76</v>
+        <v>447</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>76</v>
@@ -17338,22 +17335,22 @@
         <v>76</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>406</v>
+        <v>220</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>634</v>
+        <v>449</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>410</v>
+        <v>451</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>76</v>
@@ -17378,13 +17375,13 @@
         <v>76</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>76</v>
+        <v>452</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>76</v>
+        <v>453</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>76</v>
@@ -17402,13 +17399,13 @@
         <v>76</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>411</v>
+        <v>643</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>94</v>
@@ -17419,10 +17416,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17433,38 +17430,36 @@
         <v>74</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I147" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>414</v>
+        <v>645</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>415</v>
+        <v>646</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>273</v>
+        <v>548</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>416</v>
+        <v>549</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q147" t="s" s="2">
-        <v>417</v>
-      </c>
+      <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
         <v>76</v>
       </c>
@@ -17484,13 +17479,13 @@
         <v>76</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>418</v>
+        <v>76</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>419</v>
+        <v>76</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>76</v>
@@ -17508,647 +17503,23 @@
         <v>76</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>420</v>
+        <v>644</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="148" hidden="true">
-      <c r="A148" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="C148" s="2"/>
-      <c r="D148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E148" s="2"/>
-      <c r="F148" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G148" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J148" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K148" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="P148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q148" s="2"/>
-      <c r="R148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG148" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH148" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI148" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ148" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="149" hidden="true">
-      <c r="A149" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="C149" s="2"/>
-      <c r="D149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E149" s="2"/>
-      <c r="F149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="P149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q149" s="2"/>
-      <c r="R149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S149" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="T149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="150" hidden="true">
-      <c r="A150" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="C150" s="2"/>
-      <c r="D150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E150" s="2"/>
-      <c r="F150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J150" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K150" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="P150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q150" s="2"/>
-      <c r="R150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ150" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="151" hidden="true">
-      <c r="A151" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="P151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q151" s="2"/>
-      <c r="R151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="152" hidden="true">
-      <c r="A152" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="P152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q152" s="2"/>
-      <c r="R152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="153" hidden="true">
-      <c r="A153" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="P153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ153">
+  <autoFilter ref="A1:AJ147">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18158,7 +17529,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI152">
+  <conditionalFormatting sqref="A2:AI146">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:51:19+02:00</t>
+    <t>2026-06-26T18:38:01+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T18:38:01+02:00</t>
+    <t>2026-07-06T17:54:18+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T17:54:18+02:00</t>
+    <t>2026-07-22T15:49:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-Observation-Body-Height.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T15:49:40+02:00</t>
+    <t>2026-07-22T16:29:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
